--- a/artfynd/A 23643-2026 artfynd.xlsx
+++ b/artfynd/A 23643-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122172722</v>
+        <v>122172723</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478555</v>
+        <v>478590</v>
       </c>
       <c r="R2" t="n">
-        <v>6952908</v>
+        <v>6952855</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122172723</v>
+        <v>122172721</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478590</v>
+        <v>478547</v>
       </c>
       <c r="R3" t="n">
-        <v>6952855</v>
+        <v>6952958</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -880,6 +866,301 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122172722</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>478555</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6952908</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122172724</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>478588</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6952852</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122172702</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>478535</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6952864</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23643-2026 artfynd.xlsx
+++ b/artfynd/A 23643-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122172721</v>
+        <v>134698478</v>
       </c>
       <c r="B3" t="n">
-        <v>57874</v>
+        <v>83358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100001</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Kläppbäcken, Kläppbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478547</v>
+        <v>478601</v>
       </c>
       <c r="R3" t="n">
-        <v>6952958</v>
+        <v>6952989</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122172722</v>
+        <v>122172721</v>
       </c>
       <c r="B4" t="n">
-        <v>58057</v>
+        <v>57874</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,16 +880,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>100001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -897,21 +897,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478555</v>
+        <v>478547</v>
       </c>
       <c r="R4" t="n">
-        <v>6952908</v>
+        <v>6952958</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -970,27 +966,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122172724</v>
+        <v>122172722</v>
       </c>
       <c r="B5" t="n">
-        <v>5199</v>
+        <v>58057</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>103031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -998,17 +994,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478588</v>
+        <v>478555</v>
       </c>
       <c r="R5" t="n">
-        <v>6952852</v>
+        <v>6952908</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1067,10 +1067,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122172702</v>
+        <v>122172724</v>
       </c>
       <c r="B6" t="n">
-        <v>99035</v>
+        <v>5199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1078,21 +1078,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478535</v>
+        <v>478588</v>
       </c>
       <c r="R6" t="n">
-        <v>6952864</v>
+        <v>6952852</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1161,6 +1161,404 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122172702</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>478535</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6952864</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134699259</v>
+      </c>
+      <c r="B8" t="n">
+        <v>109924</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kläppbäcken, Kläppbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>478655</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6952959</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134698398</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kläppbäcken, Kläppbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>478599</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6952988</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134698716</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kläppbäcken, Kläppbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>478626</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6952999</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23643-2026 artfynd.xlsx
+++ b/artfynd/A 23643-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122172723</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134698478</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122172721</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122172722</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122172724</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122172702</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134699259</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134698398</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1559,8 +1604,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134698716</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>